--- a/main/ig/StructureDefinition-as-bal-mss-cab.xlsx
+++ b/main/ig/StructureDefinition-as-bal-mss-cab.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="92">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T14:23:27+00:00</t>
+    <t>2026-09-29T07:26:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -264,6 +264,15 @@
   </si>
   <si>
     <t>Adresse de messagerie MSSanté</t>
+  </si>
+  <si>
+    <t>as-bal-mss-cab.identifiantPP</t>
+  </si>
+  <si>
+    <t>Identifiant PP</t>
+  </si>
+  <si>
+    <t>Identifiant national du professionnel de santé (RPPS)</t>
   </si>
   <si>
     <t>as-bal-mss-cab.description</t>
@@ -584,11 +593,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ5"/>
+  <dimension ref="A1:AJ6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="22.0078125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="22.0078125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="23.1796875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="23.1796875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -618,7 +627,7 @@
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="22.0078125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="23.1796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -947,7 +956,7 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G4" t="s" s="2">
         <v>79</v>
@@ -965,10 +974,10 @@
         <v>80</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1022,7 +1031,7 @@
         <v>83</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH4" t="s" s="2">
         <v>79</v>
@@ -1036,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1062,13 +1071,13 @@
         <v>73</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="L5" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="M5" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="M5" t="s" s="2">
-        <v>88</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1119,7 +1128,7 @@
         <v>73</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>74</v>
@@ -1131,6 +1140,106 @@
         <v>73</v>
       </c>
       <c r="AJ5" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E6" s="2"/>
+      <c r="F6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G6" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K6" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="L6" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="M6" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q6" s="2"/>
+      <c r="R6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF6" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AG6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH6" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ6" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/main/ig/StructureDefinition-as-bal-mss-cab.xlsx
+++ b/main/ig/StructureDefinition-as-bal-mss-cab.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T07:26:07+00:00</t>
+    <t>2026-09-30T08:41:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-bal-mss-cab.xlsx
+++ b/main/ig/StructureDefinition-as-bal-mss-cab.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapshot</t>
+    <t>0.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T08:41:32+00:00</t>
+    <t>2026-10-09T06:18:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-bal-mss-cab.xlsx
+++ b/main/ig/StructureDefinition-as-bal-mss-cab.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T06:18:26+00:00</t>
+    <t>2026-10-09T06:22:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
